--- a/data/data_monitoreo_ciudad_de_dios.xlsx
+++ b/data/data_monitoreo_ciudad_de_dios.xlsx
@@ -447,27 +447,27 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>142</v>
+        <v>217</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SANCHEZ LUCUMI DIANA</t>
+          <t>TORRES ASCORBE CESAR RAMNCES</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>142</v>
+        <v>210</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>TORRES ASCORBE CESAR RAMNCES</t>
+          <t>SANCHEZ LUCUMI DIANA</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>139</v>
+        <v>195</v>
       </c>
     </row>
     <row r="5">
@@ -477,7 +477,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>127</v>
+        <v>181</v>
       </c>
     </row>
     <row r="6">
@@ -487,27 +487,27 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>120</v>
+        <v>174</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BURGA MEDINA SHIRLEY ROCIO</t>
+          <t>BLANCO LOZANO ANDREA MILAGROS</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>114</v>
+        <v>163</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BLANCO LOZANO ANDREA MILAGROS</t>
+          <t>BURGA MEDINA SHIRLEY ROCIO</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>111</v>
+        <v>162</v>
       </c>
     </row>
     <row r="9">
@@ -517,7 +517,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>111</v>
+        <v>162</v>
       </c>
     </row>
     <row r="10">
@@ -527,7 +527,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>91</v>
+        <v>117</v>
       </c>
     </row>
     <row r="11">

--- a/data/data_monitoreo_ciudad_de_dios.xlsx
+++ b/data/data_monitoreo_ciudad_de_dios.xlsx
@@ -447,7 +447,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>217</v>
+        <v>226</v>
       </c>
     </row>
     <row r="3">
@@ -457,7 +457,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>210</v>
+        <v>220</v>
       </c>
     </row>
     <row r="4">
@@ -467,7 +467,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>195</v>
+        <v>204</v>
       </c>
     </row>
     <row r="5">
@@ -477,7 +477,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>181</v>
+        <v>190</v>
       </c>
     </row>
     <row r="6">
@@ -487,7 +487,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>174</v>
+        <v>184</v>
       </c>
     </row>
     <row r="7">
@@ -497,7 +497,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="8">
@@ -507,7 +507,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="9">
@@ -517,7 +517,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="10">
@@ -527,7 +527,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>117</v>
+        <v>126</v>
       </c>
     </row>
     <row r="11">

--- a/data/data_monitoreo_ciudad_de_dios.xlsx
+++ b/data/data_monitoreo_ciudad_de_dios.xlsx
@@ -447,7 +447,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>226</v>
+        <v>230</v>
       </c>
     </row>
     <row r="3">
@@ -457,7 +457,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>220</v>
+        <v>224</v>
       </c>
     </row>
     <row r="4">
@@ -467,7 +467,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>204</v>
+        <v>207</v>
       </c>
     </row>
     <row r="5">
@@ -477,7 +477,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="6">
@@ -487,7 +487,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>184</v>
+        <v>186</v>
       </c>
     </row>
     <row r="7">
@@ -497,7 +497,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>165</v>
+        <v>176</v>
       </c>
     </row>
     <row r="8">
@@ -507,7 +507,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>164</v>
+        <v>175</v>
       </c>
     </row>
     <row r="9">
@@ -517,7 +517,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>164</v>
+        <v>174</v>
       </c>
     </row>
     <row r="10">
@@ -527,7 +527,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>126</v>
+        <v>131</v>
       </c>
     </row>
     <row r="11">

--- a/data/data_monitoreo_ciudad_de_dios.xlsx
+++ b/data/data_monitoreo_ciudad_de_dios.xlsx
@@ -447,7 +447,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>230</v>
+        <v>255</v>
       </c>
     </row>
     <row r="3">
@@ -457,7 +457,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>224</v>
+        <v>252</v>
       </c>
     </row>
     <row r="4">
@@ -467,7 +467,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>207</v>
+        <v>234</v>
       </c>
     </row>
     <row r="5">
@@ -477,7 +477,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>192</v>
+        <v>214</v>
       </c>
     </row>
     <row r="6">
@@ -487,27 +487,27 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>186</v>
+        <v>208</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BLANCO LOZANO ANDREA MILAGROS</t>
+          <t>BURGA MEDINA SHIRLEY ROCIO</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>176</v>
+        <v>200</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BURGA MEDINA SHIRLEY ROCIO</t>
+          <t>BLANCO LOZANO ANDREA MILAGROS</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>175</v>
+        <v>199</v>
       </c>
     </row>
     <row r="9">
@@ -517,7 +517,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>174</v>
+        <v>197</v>
       </c>
     </row>
     <row r="10">
@@ -527,7 +527,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>131</v>
+        <v>169</v>
       </c>
     </row>
     <row r="11">

--- a/data/data_monitoreo_ciudad_de_dios.xlsx
+++ b/data/data_monitoreo_ciudad_de_dios.xlsx
@@ -447,7 +447,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>255</v>
+        <v>263</v>
       </c>
     </row>
     <row r="3">
@@ -457,7 +457,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>252</v>
+        <v>263</v>
       </c>
     </row>
     <row r="4">
@@ -467,7 +467,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>234</v>
+        <v>241</v>
       </c>
     </row>
     <row r="5">
@@ -477,7 +477,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="6">
@@ -487,7 +487,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>208</v>
+        <v>211</v>
       </c>
     </row>
     <row r="7">
@@ -497,7 +497,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="8">
@@ -507,7 +507,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="9">
@@ -517,7 +517,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="10">
@@ -527,7 +527,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>169</v>
+        <v>175</v>
       </c>
     </row>
     <row r="11">
